--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.35580735652552</v>
+        <v>11.1078186954354</v>
       </c>
       <c r="D2" t="n">
-        <v>68.28350468256752</v>
+        <v>11.09606951091722</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53299811536226</v>
+        <v>2.686612193746368</v>
       </c>
       <c r="F2" t="n">
-        <v>16.4163510258444</v>
+        <v>2.667657041699716</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.60404358330888</v>
+        <v>9.848157082287694</v>
       </c>
       <c r="D3" t="n">
-        <v>60.6014241412687</v>
+        <v>9.847731422956164</v>
       </c>
       <c r="E3" t="n">
-        <v>16.53299811536226</v>
+        <v>2.686612193746368</v>
       </c>
       <c r="F3" t="n">
-        <v>16.4163510258444</v>
+        <v>2.667657041699716</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.59625697913712</v>
+        <v>8.384391759109782</v>
       </c>
       <c r="D4" t="n">
-        <v>51.55597060240802</v>
+        <v>8.377845222891303</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53299811536226</v>
+        <v>2.686612193746368</v>
       </c>
       <c r="F4" t="n">
-        <v>16.4163510258444</v>
+        <v>2.667657041699716</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.76100801113962</v>
+        <v>3.373663801810188</v>
       </c>
       <c r="D5" t="n">
-        <v>21.30857791289116</v>
+        <v>3.462643910844814</v>
       </c>
       <c r="E5" t="n">
-        <v>16.53299811536226</v>
+        <v>2.686612193746368</v>
       </c>
       <c r="F5" t="n">
-        <v>16.4163510258444</v>
+        <v>2.667657041699716</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.64842799374773</v>
+        <v>6.767869548984007</v>
       </c>
       <c r="D6" t="n">
-        <v>40.69361559443743</v>
+        <v>6.612712534096083</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53299811536226</v>
+        <v>2.686612193746368</v>
       </c>
       <c r="F6" t="n">
-        <v>16.4163510258444</v>
+        <v>2.667657041699716</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
